--- a/target/差异上架表.xlsx
+++ b/target/差异上架表.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,42 +460,42 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>供应商名称</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>上架库位</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>差异日期</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>库位编码</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>未锁账数量</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>锁帐数量</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>总库存数量</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>供应商编码</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>供应商名称</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -611,56 +611,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45237.74836805555</v>
+        <v>45246.72643518518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>YG9725190143/1</t>
+          <t>712W25441-5342/2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YG9725190143</t>
+          <t>712W25441-5342</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>油滤器前支架</t>
+          <t>左导线槽安装支架</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>312302.C07.460101</t>
+          <t>济南东冠汽车零部件有限公司</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>312302.C25.050101</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>312302.S01.010101</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>30</v>
-      </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="L2" t="n">
-        <v>101753</v>
+        <v>42</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>济南汇英机械有限公司</t>
+          <t>101595</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -699,12 +701,14 @@
           <t>平面库存储区</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>101753</v>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>101595</t>
+        </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>济南汇英机械有限公司</t>
+          <t>济南东冠汽车零部件有限公司</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -714,20 +718,20 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>23110701</v>
+        <v>23111601</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>PH202311073594</t>
+          <t>PH202311161688</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>TP20231107471833</t>
+          <t>TP20231116230440</t>
         </is>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>45237.74793981481</v>
+        <v>45246.72546296296</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -736,62 +740,64 @@
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" s="2" t="n">
-        <v>45237.74834490741</v>
+        <v>45246.72641203704</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>耿叶永</t>
+          <t>刘兵</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45237.62570601852</v>
+        <v>45246.56657407407</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WG9525850002/2</t>
+          <t>WG9925190133/1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WG9525850002</t>
+          <t>WG9925190133</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>灭火器支架总成</t>
+          <t>垫块</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>内饰</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+          <t>济南晋升汽车配件厂</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>312302.C02.030902</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>312302.S01.010101</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="L3" t="n">
-        <v>101261</v>
+        <v>150</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>河北华特汽车部件有限公司</t>
+          <t>101822</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -830,12 +836,14 @@
           <t>平面库存储区</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>101261</v>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>101822</t>
+        </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>河北华特汽车部件有限公司</t>
+          <t>济南晋升汽车配件厂</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -845,289 +853,33 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>23110701</v>
+        <v>23111601</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>PH202311071173</t>
+          <t>PH202311160808</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>TP20231107359293</t>
+          <t>TP20231116107167</t>
         </is>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>45237.62297453704</v>
+        <v>45246.56636574074</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" s="2" t="n">
-        <v>45237.62568287037</v>
+        <v>45246.56655092593</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>刘兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45237.68990740741</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AZ962547000103/2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AZ962547000103</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>支架</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>总装</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>312302.S01.010101</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>20</v>
-      </c>
-      <c r="L4" t="n">
-        <v>100563</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>沧州大华金属制品有限公司</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>312302</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>制造部平面仓储库</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>待检</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>312302.S01</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1004库来料暂存区</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>平面库存储区</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>100563</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>沧州大华金属制品有限公司</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>托管</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>23110701</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>PH202311073413</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>TP20231107448563</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>45237.68962962963</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" s="2" t="n">
-        <v>45237.68988425926</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>刘兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45237.74762731481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>WG9525470050/3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>WG9525470050</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>D50方向机</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>312302.C09.780101</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>312302.S01.010101</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>96</v>
-      </c>
-      <c r="K5" t="n">
-        <v>96</v>
-      </c>
-      <c r="L5" t="n">
-        <v>103298</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>全兴精工集团有限公司</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>312302</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>制造部平面仓储库</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>待检</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>312302.S01</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1004库来料暂存区</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>平面库存储区</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>103298</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>全兴精工集团有限公司</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>托管</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
-        <v>23110701</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>PH202311073593</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>TP20231107471831</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="n">
-        <v>45237.74736111111</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" s="2" t="n">
-        <v>45237.74760416667</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>耿叶永</t>
         </is>
       </c>
     </row>
